--- a/AI Audit Log_LeNguyenMinhTai_DE190621.xlsx
+++ b/AI Audit Log_LeNguyenMinhTai_DE190621.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\FBT_UNIVERSITY\FBT_UNIVERSITY_KI_7\SWD392\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C664900E-9531-4DE4-A98D-EB7B2454E233}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{682ACBEB-2AB5-4CD6-9BD2-0D389E9DCB7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{84C35D15-8A6C-4EDA-8B49-2CCD89DED56E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{84C35D15-8A6C-4EDA-8B49-2CCD89DED56E}"/>
   </bookViews>
   <sheets>
     <sheet name="Template" sheetId="1" r:id="rId1"/>
-    <sheet name="Assigment1" sheetId="5" r:id="rId2"/>
+    <sheet name="Week 1" sheetId="5" r:id="rId2"/>
+    <sheet name="Week 2" sheetId="6" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="37">
   <si>
     <t>Ví dụ: Abstraction</t>
   </si>
@@ -141,6 +142,48 @@
   <si>
     <t xml:space="preserve">Phản hồi: Mô hình hóa phần mềm (Software Modeling) là quá trình thiết kế và mô tả hệ thống phần mềm trước khi lập trình, giúp nhóm phát triển hiểu rõ yêu cầu, phân tích bài toán và xây dựng giải pháp phù hợp trước khi coding. Trong quá trình này, UML (Unified Modeling Language) thường được sử dụng để trực quan hóa hệ thống. Theo phương pháp COMET, mô hình hóa phần mềm gồm 3 giai đoạn chính. Mô hình hóa yêu cầu (Requirements Modeling) tập trung xác định hệ thống cần cung cấp những chức năng gì cho người dùng thông qua actor và use case, đồng thời xem xét các yêu cầu phi chức năng như hiệu năng và bảo mật. Mô hình hóa phân tích (Analysis Modeling) tập trung vào việc hiểu miền bài toán bằng cách xác định các lớp, đối tượng, mối quan hệ và cách các đối tượng tương tác hoặc thay đổi trạng thái thông qua các biểu đồ UML. Mô hình hóa thiết kế (Design Modeling) là giai đoạn chuyển từ phân tích sang giải pháp thực tế, bao gồm thiết kế kiến trúc hệ thống, chia hệ thống thành các subsystem, xác định interface giữa các thành phần, và lựa chọn các architectural patterns hoặc design patterns phù hợp. Kết quả cuối cùng là một bản thiết kế hoàn chỉnh để làm nền tảng cho việc lập trình, tích hợp và kiểm thử hệ thống.
 Kiểm chứng: AI đưa ra chính xác các bước trong phát triển phần mềm </t>
+  </si>
+  <si>
+    <t>Ví dụ: Sơ đồ usecase là gì và nó dùng để làm gì?</t>
+  </si>
+  <si>
+    <t>Sơ đồ usecase là gì và nó dùng để làm gì</t>
+  </si>
+  <si>
+    <t>Phản hồi: Sơ đồ Use Case là một loại sơ đồ trong UML dùng để mô tả cách người dùng (actor) tương tác với hệ thống nhằm thực hiện các chức năng cụ thể. Nó giúp xác định hệ thống sẽ làm gì từ góc nhìn của người dùng thay vì tập trung vào cách hệ thống hoạt động bên trong. Sơ đồ Use Case thường được sử dụng trong giai đoạn phân tích và thiết kế phần mềm để thu thập yêu cầu, giao tiếp giữa khách hàng và nhóm phát triển, đồng thời giúp lập trình viên hiểu rõ các chức năng cần xây dựng trong hệ thống.
+Quyết định: Tôi đọc và tham khảo tất cả các tính chất mà ChatGPT đưa ra, đồng thời tham khảo từ nhiều trang web uy tín</t>
+  </si>
+  <si>
+    <t>Ví dụ: Sơ đồ usecase gồm những phần nào</t>
+  </si>
+  <si>
+    <t>Sơ đồ usecase gồm những phần nào</t>
+  </si>
+  <si>
+    <t>Phản hồi: Sơ đồ Use Case thường gồm các thành phần chính sau:
+Actor (Tác nhân): Đại diện cho người dùng hoặc hệ thống bên ngoài tương tác với hệ thống, ví dụ: khách hàng, quản trị viên, cổng thanh toán.
+Use Case: Các chức năng hoặc nghiệp vụ mà hệ thống cung cấp, được biểu diễn bằng hình elip, ví dụ: đăng nhập, đặt hàng, thanh toán.
+System Boundary (Ranh giới hệ thống): Khung chữ nhật bao quanh các Use Case để xác định phạm vi của hệ thống.
+Relationship (Mối quan hệ): Thể hiện sự liên kết giữa các thành phần, gồm:
+Association: Quan hệ tương tác giữa actor và use case.
+Include: Một use case luôn sử dụng lại chức năng của use case khác.
+Extend: Một use case mở rộng thêm hành vi cho use case khác trong trường hợp đặc biệt.
+Generalization: Quan hệ kế thừa giữa các actor hoặc use case.
+Kiểm chứng: Tôi đọc và kiểm chứng từ sách, AI đã đưa ra đầy đủ các phần</t>
+  </si>
+  <si>
+    <t>Phản hồi: Trong sơ đồ Use Case, Include và Extend đều là mối quan hệ giữa các use case, nhưng mục đích sử dụng khác nhau.
+Include dùng khi một use case luôn phải gọi một use case khác để thực hiện chức năng chung. Nó giúp tái sử dụng phần xử lý lặp lại nhiều lần. Quan hệ này mang tính bắt buộc.
+Ví dụ: Use case “Đặt hàng” luôn phải thực hiện “Đăng nhập”, nên “Đặt hàng” sẽ include “Đăng nhập”.
+Extend dùng khi một use case chỉ mở rộng thêm hành vi trong điều kiện đặc biệt hoặc tùy chọn. Use case chính vẫn có thể hoạt động bình thường mà không cần phần mở rộng. Quan hệ này mang tính không bắt buộc.
+Ví dụ: Use case “Thanh toán” có thể extend “Sử dụng mã giảm giá”, vì người dùng có thể nhập mã hoặc không.
+Kiểm chứng: Dựa theo những tính chất và ví dụ có trong sách, tôi thấy ví dụ của AI đưa ra khá chính xác</t>
+  </si>
+  <si>
+    <t>Ví dụ: giải thích và phân biệt mối quan hệ include và extend</t>
+  </si>
+  <si>
+    <t>giải thích và phân biệt mối quan hệ include và extend</t>
   </si>
 </sst>
 </file>
@@ -200,7 +243,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -228,6 +271,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -564,15 +610,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFBDDC7E-59F2-4CBB-B3D2-F6FB78F9E873}">
   <dimension ref="A1:E5"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="20.8984375" customWidth="1"/>
-    <col min="2" max="2" width="26.8984375" customWidth="1"/>
-    <col min="3" max="3" width="24.296875" customWidth="1"/>
+    <col min="1" max="1" width="20.875" customWidth="1"/>
+    <col min="2" max="2" width="26.875" customWidth="1"/>
+    <col min="3" max="3" width="24.25" customWidth="1"/>
     <col min="4" max="4" width="45" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" ht="15">
       <c r="A1" s="5" t="s">
         <v>10</v>
       </c>
@@ -587,7 +633,7 @@
       </c>
       <c r="E1" s="1"/>
     </row>
-    <row r="2" spans="1:5" ht="69">
+    <row r="2" spans="1:5" ht="71.25">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -601,7 +647,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="55.2">
+    <row r="3" spans="1:5" ht="71.25">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -615,7 +661,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="69">
+    <row r="4" spans="1:5" ht="71.25">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -629,7 +675,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="82.8">
+    <row r="5" spans="1:5" ht="85.5">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -651,15 +697,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22539089-848F-48AB-A297-CCCDF9986DC6}">
   <dimension ref="A1:E5"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="20.8984375" customWidth="1"/>
+    <col min="1" max="1" width="20.875" customWidth="1"/>
     <col min="2" max="2" width="32" customWidth="1"/>
     <col min="3" max="3" width="30.5" customWidth="1"/>
-    <col min="4" max="4" width="165.3984375" customWidth="1"/>
+    <col min="4" max="4" width="165.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="22.8" customHeight="1">
+    <row r="1" spans="1:5" ht="22.9" customHeight="1">
       <c r="A1" s="8" t="s">
         <v>10</v>
       </c>
@@ -674,7 +720,7 @@
       </c>
       <c r="E1" s="1"/>
     </row>
-    <row r="2" spans="1:5" ht="253.2" customHeight="1">
+    <row r="2" spans="1:5" ht="253.15" customHeight="1">
       <c r="A2" s="9">
         <v>1</v>
       </c>
@@ -702,7 +748,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="110.4">
+    <row r="4" spans="1:5" ht="114">
       <c r="A4" s="9">
         <v>3</v>
       </c>
@@ -729,6 +775,82 @@
       <c r="D5" s="7" t="s">
         <v>27</v>
       </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{730C5B6F-A6D6-4A22-B985-6352BA47C4CC}">
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
+  <cols>
+    <col min="1" max="1" width="20.875" customWidth="1"/>
+    <col min="2" max="2" width="32" customWidth="1"/>
+    <col min="3" max="3" width="30.5" customWidth="1"/>
+    <col min="4" max="4" width="165.375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="22.9" customHeight="1">
+      <c r="A1" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E1" s="1"/>
+    </row>
+    <row r="2" spans="1:5" ht="81.75" customHeight="1">
+      <c r="A2" s="9">
+        <v>1</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="144" customHeight="1">
+      <c r="A3" s="9">
+        <v>2</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="99.75">
+      <c r="A4" s="9">
+        <v>3</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="44.25" customHeight="1">
+      <c r="A5" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AI Audit Log_LeNguyenMinhTai_DE190621.xlsx
+++ b/AI Audit Log_LeNguyenMinhTai_DE190621.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\FBT_UNIVERSITY\FBT_UNIVERSITY_KI_7\SWD392\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{682ACBEB-2AB5-4CD6-9BD2-0D389E9DCB7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55525813-E7C3-45C5-B0DE-DA556D463336}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{84C35D15-8A6C-4EDA-8B49-2CCD89DED56E}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{84C35D15-8A6C-4EDA-8B49-2CCD89DED56E}"/>
   </bookViews>
   <sheets>
     <sheet name="Template" sheetId="1" r:id="rId1"/>
     <sheet name="Week 1" sheetId="5" r:id="rId2"/>
     <sheet name="Week 2" sheetId="6" r:id="rId3"/>
+    <sheet name="Week 3" sheetId="7" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="37">
   <si>
     <t>Ví dụ: Abstraction</t>
   </si>
@@ -610,15 +611,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFBDDC7E-59F2-4CBB-B3D2-F6FB78F9E873}">
   <dimension ref="A1:E5"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="20.875" customWidth="1"/>
-    <col min="2" max="2" width="26.875" customWidth="1"/>
-    <col min="3" max="3" width="24.25" customWidth="1"/>
+    <col min="1" max="1" width="20.8984375" customWidth="1"/>
+    <col min="2" max="2" width="26.8984375" customWidth="1"/>
+    <col min="3" max="3" width="24.19921875" customWidth="1"/>
     <col min="4" max="4" width="45" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15">
+    <row r="1" spans="1:5">
       <c r="A1" s="5" t="s">
         <v>10</v>
       </c>
@@ -633,7 +634,7 @@
       </c>
       <c r="E1" s="1"/>
     </row>
-    <row r="2" spans="1:5" ht="71.25">
+    <row r="2" spans="1:5" ht="69">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -647,7 +648,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="71.25">
+    <row r="3" spans="1:5" ht="55.2">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -661,7 +662,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="71.25">
+    <row r="4" spans="1:5" ht="69">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -675,7 +676,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="85.5">
+    <row r="5" spans="1:5" ht="82.8">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -697,15 +698,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22539089-848F-48AB-A297-CCCDF9986DC6}">
   <dimension ref="A1:E5"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="20.875" customWidth="1"/>
+    <col min="1" max="1" width="20.8984375" customWidth="1"/>
     <col min="2" max="2" width="32" customWidth="1"/>
     <col min="3" max="3" width="30.5" customWidth="1"/>
-    <col min="4" max="4" width="165.375" customWidth="1"/>
+    <col min="4" max="4" width="165.3984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="22.9" customHeight="1">
+    <row r="1" spans="1:5" ht="22.95" customHeight="1">
       <c r="A1" s="8" t="s">
         <v>10</v>
       </c>
@@ -720,7 +721,7 @@
       </c>
       <c r="E1" s="1"/>
     </row>
-    <row r="2" spans="1:5" ht="253.15" customHeight="1">
+    <row r="2" spans="1:5" ht="253.2" customHeight="1">
       <c r="A2" s="9">
         <v>1</v>
       </c>
@@ -748,7 +749,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="114">
+    <row r="4" spans="1:5" ht="110.4">
       <c r="A4" s="9">
         <v>3</v>
       </c>
@@ -784,15 +785,15 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{730C5B6F-A6D6-4A22-B985-6352BA47C4CC}">
   <dimension ref="A1:E5"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="20.875" customWidth="1"/>
+    <col min="1" max="1" width="20.8984375" customWidth="1"/>
     <col min="2" max="2" width="32" customWidth="1"/>
     <col min="3" max="3" width="30.5" customWidth="1"/>
-    <col min="4" max="4" width="165.375" customWidth="1"/>
+    <col min="4" max="4" width="165.3984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="22.9" customHeight="1">
+    <row r="1" spans="1:5" ht="22.95" customHeight="1">
       <c r="A1" s="8" t="s">
         <v>10</v>
       </c>
@@ -835,7 +836,83 @@
         <v>33</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="99.75">
+    <row r="4" spans="1:5" ht="96.6">
+      <c r="A4" s="9">
+        <v>3</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="44.25" customHeight="1">
+      <c r="A5" s="9"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B5226B1-0610-4C4F-B69A-588847FC96C3}">
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
+  <cols>
+    <col min="1" max="1" width="20.8984375" customWidth="1"/>
+    <col min="2" max="2" width="32" customWidth="1"/>
+    <col min="3" max="3" width="30.5" customWidth="1"/>
+    <col min="4" max="4" width="165.3984375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="22.95" customHeight="1">
+      <c r="A1" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E1" s="1"/>
+    </row>
+    <row r="2" spans="1:5" ht="81.75" customHeight="1">
+      <c r="A2" s="9">
+        <v>1</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="144" customHeight="1">
+      <c r="A3" s="9">
+        <v>2</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="96.6">
       <c r="A4" s="9">
         <v>3</v>
       </c>

--- a/AI Audit Log_LeNguyenMinhTai_DE190621.xlsx
+++ b/AI Audit Log_LeNguyenMinhTai_DE190621.xlsx
@@ -8,15 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\FBT_UNIVERSITY\FBT_UNIVERSITY_KI_7\SWD392\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55525813-E7C3-45C5-B0DE-DA556D463336}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBE95FCE-3687-461D-8A35-BEE3E816C0CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{84C35D15-8A6C-4EDA-8B49-2CCD89DED56E}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{84C35D15-8A6C-4EDA-8B49-2CCD89DED56E}"/>
   </bookViews>
   <sheets>
     <sheet name="Template" sheetId="1" r:id="rId1"/>
     <sheet name="Week 1" sheetId="5" r:id="rId2"/>
     <sheet name="Week 2" sheetId="6" r:id="rId3"/>
     <sheet name="Week 3" sheetId="7" r:id="rId4"/>
+    <sheet name="Week 4" sheetId="8" r:id="rId5"/>
+    <sheet name="Week 5" sheetId="10" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="52">
   <si>
     <t>Ví dụ: Abstraction</t>
   </si>
@@ -186,12 +188,283 @@
   <si>
     <t>giải thích và phân biệt mối quan hệ include và extend</t>
   </si>
+  <si>
+    <t>Abstraction</t>
+  </si>
+  <si>
+    <t>"Dựa trên yêu cầu đề bài về hệ thống quản lý nhà hàng, hãy xác định các lớp chính, thuộc tính và mối quan hệ cần có trong Class Diagram theo Layered Architecture và Repository Pattern."</t>
+  </si>
+  <si>
+    <r>
+      <t>Phản hồi:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> AI đề xuất các lớp: User, Customer, Staff, Chef, Menu, MenuItem, Order, OrderItem, Payment, OrderService, PaymentService, Repository, OrderRepository, PaymentRepository. Đồng thời gợi ý các quan hệ inheritance, composition và dependency. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Quyết định:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Tôi giữ lại các thực thể nghiệp vụ và lớp service/repository phù hợp với đề bài, nhưng loại bỏ một số lớp AI đề xuất thêm như NotificationService vì không nằm trong phạm vi yêu cầu của đề thi.</t>
+    </r>
+  </si>
+  <si>
+    <t>Decomposition / Process Design</t>
+  </si>
+  <si>
+    <t>"Hãy mô tả luồng xử lý cho use case 'Place Order and Pay' theo Layered Architecture để tôi xây dựng Sequence Diagram."</t>
+  </si>
+  <si>
+    <r>
+      <t>Phản hồi:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> AI đưa ra luồng: Customer App → OrderController → OrderService → OrderRepository → PaymentService → PaymentRepository → KitchenService. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Quyết định:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Tôi sử dụng luồng này làm cơ sở cho Sequence Diagram nhưng bổ sung thêm các đối tượng domain như Order và Payment theo yêu cầu đề bài. Tôi cũng thêm alt fragment cho hai trường hợp Payment Success và Payment Failure để đáp ứng đầy đủ tiêu chí chấm điểm.</t>
+    </r>
+  </si>
+  <si>
+    <t>Pattern Recognition</t>
+  </si>
+  <si>
+    <t>"Dựa trên Repository Pattern, hãy cho biết những thành phần nào trong hệ thống cần triển khai interface Repository và giải thích lý do."</t>
+  </si>
+  <si>
+    <r>
+      <t>Phản hồi:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> AI đề xuất OrderRepository, PaymentRepository, MenuRepository và CustomerRepository kế thừa Repository. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Kiểm chứng:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Tôi đối chiếu lại đề thi và nhận thấy đề chỉ yêu cầu thể hiện rõ việc áp dụng Repository Pattern chứ không bắt buộc tất cả repository phải xuất hiện. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Quyết định:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Tôi chỉ sử dụng các repository liên quan trực tiếp đến luồng nghiệp vụ chính như OrderRepository và PaymentRepository để tránh làm sơ đồ quá phức tạp.</t>
+    </r>
+  </si>
+  <si>
+    <t>Algorithm / Process Modeling</t>
+  </si>
+  <si>
+    <t>"Hãy xác định các trạng thái và sự kiện chuyển trạng thái của Order trong hệ thống quản lý nhà hàng theo yêu cầu đề bài."</t>
+  </si>
+  <si>
+    <r>
+      <t>Phản hồi:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> AI đề xuất các trạng thái: Created → Confirmed → Paid → Preparing → ReadyToServe → Served → Completed; nhánh phụ gồm PaymentFailed và Cancelled. Các sự kiện bao gồm confirmOrder, paySuccess, payFail, startCooking, finishCooking, serveOrder và closeOrder. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Quyết định:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Tôi sử dụng đầy đủ các trạng thái này vì phù hợp với yêu cầu đề. Tuy nhiên, tôi bổ sung trạng thái Cancelled như một final state thay thế để biểu diễn trường hợp đơn hàng bị hủy.</t>
+    </r>
+  </si>
+  <si>
+    <t>Evaluation / Critical Thinking</t>
+  </si>
+  <si>
+    <t>"Kiểm tra xem Class Diagram và Sequence Diagram của tôi đã đáp ứng đầy đủ các yêu cầu trong đề thi hay chưa. Hãy liệt kê những điểm còn thiếu."</t>
+  </si>
+  <si>
+    <r>
+      <t>Phản hồi:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> AI kiểm tra và chỉ ra rằng Sequence Diagram còn thiếu alt fragment cho Payment Failure và Class Diagram chưa thể hiện rõ dependency giữa Service và Repository. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Kiểm chứng:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Tôi so sánh với checklist trong đề thi và xác nhận nhận xét của AI là chính xác. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Quyết định:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Tôi chỉnh sửa sơ đồ bằng cách thêm dependency relationship giữa service và repository, đồng thời bổ sung alt fragment để thể hiện đầy đủ hai trường hợp thanh toán thành công và thất bại.</t>
+    </r>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -206,6 +479,15 @@
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <charset val="163"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -244,7 +526,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -275,6 +557,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -932,4 +1217,180 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1550743D-50D7-4810-85C5-9A2C519A4214}">
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
+  <cols>
+    <col min="1" max="1" width="20.8984375" customWidth="1"/>
+    <col min="2" max="2" width="32" customWidth="1"/>
+    <col min="3" max="3" width="30.5" customWidth="1"/>
+    <col min="4" max="4" width="165.3984375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="22.95" customHeight="1">
+      <c r="A1" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E1" s="1"/>
+    </row>
+    <row r="2" spans="1:5" ht="81.75" customHeight="1">
+      <c r="A2" s="9">
+        <v>1</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="144" customHeight="1">
+      <c r="A3" s="9">
+        <v>2</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="96.6">
+      <c r="A4" s="9">
+        <v>3</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="44.25" customHeight="1">
+      <c r="A5" s="9"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67402957-B362-4342-9AD2-B4F426FC8AB1}">
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
+  <cols>
+    <col min="1" max="1" width="9.3984375" customWidth="1"/>
+    <col min="2" max="2" width="22.8984375" customWidth="1"/>
+    <col min="3" max="3" width="24.3984375" customWidth="1"/>
+    <col min="4" max="4" width="47" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="47.4" customHeight="1">
+      <c r="A1" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1" s="11" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="131.4" customHeight="1">
+      <c r="A2" s="11">
+        <v>1</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="124.2">
+      <c r="A3" s="11">
+        <v>2</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="124.2">
+      <c r="A4" s="11">
+        <v>3</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="138">
+      <c r="A5" s="11">
+        <v>4</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="124.2">
+      <c r="A6" s="11">
+        <v>5</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>51</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>